--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,12 +662,189 @@
           <t>NSE:HDFCBANK26AUG730PE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:16:55</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>402</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H3" t="n">
+        <v>400</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10752</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="U3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:NATIONALUM26AUG400CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:16:55</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8513.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I4" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="K4" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="L4" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="M4" t="n">
+        <v>139.76</v>
+      </c>
+      <c r="N4" t="n">
+        <v>900</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:DIVISLAB26AUG8500CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,6 +843,100 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:DIVISLAB26AUG8500CE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:18:32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>111.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>112</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20491</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S5" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="U5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:VMM26AUG112.5PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,101 @@
           <t>NSE:VMM26AUG112.5PE</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:20:10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3963.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3950</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K6" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="L6" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>101.61</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1416</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="S6" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="U6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:SIEMENS26AUG3950CE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,12 +1028,101 @@
           <t>NSE:SIEMENS26AUG3950CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:21:46</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4341.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4350</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2538</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="U7" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:TVSMOTOR26AUG4350CE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,12 +1117,101 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:23:31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5669</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K8" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="L8" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="M8" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2506</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="U8" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -845,11 +845,7 @@
           <t>NSE:DIVISLAB26AUG8500CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:18:32</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1206,12 +1202,6 @@
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -845,7 +845,6 @@
           <t>NSE:DIVISLAB26AUG8500CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1200,6 +1199,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:28:56</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:33:55</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1199,11 +1204,6 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:28:56</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,11 +756,7 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:33:55</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,7 +756,11 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:37:06</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1200,6 +1204,95 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:37:06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1544.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1540</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K9" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="M9" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3663</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Plastics</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:ASTRAL26AUG1540CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1028,6 +1028,16 @@
           <t>NSE:SIEMENS26AUG3950CE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:39:03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,11 +756,7 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:37:06</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,7 +756,6 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1299,6 +1298,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:ASTRAL26AUG1540CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:42:26</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1028,9 +1028,14 @@
           <t>2026-08-24 09:39:03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:43:04</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1038,6 +1038,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:44:02</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1127,6 +1132,11 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:44:02</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1303,11 +1313,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:ASTRAL26AUG1540CE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:42:26</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1132,11 +1132,6 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:44:02</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1313,6 +1308,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:ASTRAL26AUG1540CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:45:10</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1038,11 +1038,7 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:44:02</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1038,7 +1038,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1215,6 +1214,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:49:58</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1127,6 +1127,11 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:51:34</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1315,11 +1315,7 @@
           <t>NSE:ASTRAL26AUG1540CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:45:10</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1315,7 +1315,11 @@
           <t>NSE:ASTRAL26AUG1540CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:54:45</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -934,6 +934,11 @@
           <t>NSE:VMM26AUG112.5PE</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:56:20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:57:56</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -932,11 +937,6 @@
       <c r="W5" t="inlineStr">
         <is>
           <t>NSE:VMM26AUG112.5PE</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:56:20</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,11 +756,7 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:57:56</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -756,7 +756,6 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -933,6 +932,16 @@
       <c r="W5" t="inlineStr">
         <is>
           <t>NSE:VMM26AUG112.5PE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:02:33</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -944,6 +944,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:04:15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1142,6 +1142,16 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:08:03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-24 09:51:34</t>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1053,6 +1053,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:08:59</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1338,11 +1343,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:ASTRAL26AUG1540CE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:54:45</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,6 +1343,100 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:ASTRAL26AUG1540CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:10:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:10:35</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5464</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,9 +1048,14 @@
           <t>2026-08-24 09:43:04</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:18:31</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1437,6 +1442,100 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>NSE:LODHA26AUG1260CE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:18:30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1053.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1060</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="L11" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="M11" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8403</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="S11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1058,11 +1058,7 @@
           <t>Target 3 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:08:59</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1058,7 +1058,6 @@
           <t>Target 3 Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1440,11 +1439,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:18:30</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1152,9 +1152,14 @@
           <t>2026-08-24 10:08:03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:22:56</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1439,7 +1444,6 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1533,6 +1533,101 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:23:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7533</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I12" t="n">
+        <v>73.55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="K12" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>147.31</v>
+      </c>
+      <c r="M12" t="n">
+        <v>184.19</v>
+      </c>
+      <c r="N12" t="n">
+        <v>679</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="S12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:ABB26AUG7500CE</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1444,6 +1444,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:24:53</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1622,12 +1627,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1444,11 +1444,6 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:24:53</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1625,6 +1620,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:ABB26AUG7500CE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:28:04</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,11 @@
           <t>Target 3 Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29:40</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1622,9 +1627,93 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:28:04</t>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29:40</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1307.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="M13" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4587</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="S13" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1627,6 +1627,11 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:31:16</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1721,6 +1721,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:32:51</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1721,11 +1721,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:32:51</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1449,6 +1449,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:37:35</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1721,7 +1726,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,6 +1724,100 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:JSWSTEEL26AUG1300CE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:39:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:39:10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>114.53</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>115</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22831</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="U14" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:VMM26AUG115PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1726,11 +1726,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:39:10</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1632,11 +1632,7 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:31:16</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1726,7 +1722,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1632,7 +1632,11 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:44:05</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1632,11 +1632,7 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:44:05</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1449,11 +1449,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:37:35</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1632,7 +1628,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -845,6 +845,11 @@
           <t>NSE:DIVISLAB26AUG8500CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:56:43</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1449,7 +1454,6 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:HDFCBANK26AUG730PE</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:59:48</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-24 09:16:55</t>
@@ -845,11 +855,7 @@
           <t>NSE:DIVISLAB26AUG8500CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:56:43</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -855,7 +855,6 @@
           <t>NSE:DIVISLAB26AUG8500CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1460,6 +1459,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:04:05</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1636,6 +1640,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:ABB26AUG7500CE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:04:05</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1642,11 +1642,7 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:04:05</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,11 @@
           <t>NSE:DIVISLAB26AUG8500CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:07:16</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1642,7 +1647,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1819,6 +1823,95 @@
       <c r="W14" t="inlineStr">
         <is>
           <t>NSE:VMM26AUG115PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:07:15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>86</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N15" t="n">
+        <v>125000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="S15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="U15" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:IDFCFIRSTB26AUG86CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -667,9 +667,14 @@
           <t>2026-08-24 10:59:48</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:10:27</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1645,6 +1650,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:ABB26AUG7500CE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:10:27</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1746,6 +1746,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:15:12</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1922,6 +1927,11 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>NSE:IDFCFIRSTB26AUG86CE</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:15:12</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1840,6 +1840,16 @@
           <t>NSE:VMM26AUG115PE</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:16:30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1652,11 +1652,7 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:10:27</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1652,7 +1652,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1742,11 +1741,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:15:12</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,11 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:24:40</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1741,7 +1746,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1933,6 +1937,95 @@
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-24 11:15:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:24:40</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H16" t="n">
+        <v>115</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>71428</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="S16" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NSE:PNB26AUG115CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1652,11 +1652,7 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:24:40</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1652,7 +1652,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2022,6 +2021,11 @@
       <c r="W16" t="inlineStr">
         <is>
           <t>NSE:PNB26AUG115CE</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:27:51</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1741,6 +1741,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:29:27</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1838,6 +1843,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:29:27</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1845,11 +1845,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:29:27</t>
-        </is>
-      </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -672,9 +672,14 @@
           <t>2026-08-24 11:10:27</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:31:56</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1845,7 +1850,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1657,6 +1657,11 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:32:38</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1657,11 +1657,7 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:32:38</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1187,9 +1187,14 @@
           <t>2026-08-24 10:22:56</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:48:50</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1657,7 +1662,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1855,6 +1855,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:50:02</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1662,6 +1662,11 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:51:36</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1853,11 +1858,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>Target 1 Hit</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:50:02</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,11 +1756,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:29:27</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,7 +1756,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1851,9 +1850,14 @@
           <t>2026-08-24 11:16:30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:03:56</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1662,11 +1662,6 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:51:36</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1754,6 +1749,11 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:JSWSTEEL26AUG1300CE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:08:55</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1751,11 +1751,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:08:55</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1662,6 +1662,11 @@
           <t>NSE:ABB26AUG7500CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:13:40</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1751,7 +1756,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2042,6 +2046,95 @@
       <c r="AC16" t="inlineStr">
         <is>
           <t>2026-08-24 11:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:13:40</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5452.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I17" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K17" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="L17" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>91.06999999999999</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1669</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="S17" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="U17" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NSE:KEI26AUG5500CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,6 +1756,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:16:51</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,11 +1756,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:16:51</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,7 +1756,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2136,6 +2135,11 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>NSE:KEI26AUG5500CE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:21:43</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,6 +1756,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:28:02</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2140,6 +2145,95 @@
       <c r="AC17" t="inlineStr">
         <is>
           <t>2026-08-24 12:21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:28:02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>966.85</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>960</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4149</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="S18" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="U18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NSE:KFINTECH26AUG960CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,11 +1756,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:28:02</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2234,6 +2229,11 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>NSE:KFINTECH26AUG960CE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:29:37</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,6 +1756,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:45</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2229,11 +2234,6 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>NSE:KFINTECH26AUG960CE</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:29:37</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2236,6 +2236,11 @@
           <t>NSE:KFINTECH26AUG960CE</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:34:19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,11 +1756,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:32:45</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -776,6 +776,11 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:42:13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1756,7 +1761,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -776,11 +776,7 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:42:13</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -776,7 +776,6 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2232,11 +2231,7 @@
           <t>NSE:KFINTECH26AUG960CE</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:34:19</t>
-        </is>
-      </c>
+      <c r="AC18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2231,7 +2231,11 @@
           <t>NSE:KFINTECH26AUG960CE</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:53:11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,6 +1756,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:07:22</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2234,6 +2239,95 @@
       <c r="AC18" t="inlineStr">
         <is>
           <t>2026-08-24 12:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:07:22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="H19" t="n">
+        <v>355</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17857</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="S19" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="U19" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>NSE:FEDERALBNK26AUG355CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,11 +1756,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-24 13:07:22</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1756,7 +1756,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:15:16</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1865,6 +1865,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:24:42</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1865,11 +1865,7 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-08-24 13:24:42</t>
-        </is>
-      </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1865,7 +1865,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2329,6 +2328,11 @@
       <c r="W19" t="inlineStr">
         <is>
           <t>NSE:FEDERALBNK26AUG355CE</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:30:59</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,6 +2335,101 @@
           <t>2026-08-24 13:30:59</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:03:21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1312.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="M20" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4587</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="S20" t="n">
+        <v>28</v>
+      </c>
+      <c r="T20" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NSE:JSWSTEEL26AUG1300CE</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,12 +2424,100 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:04:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:04:57</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1259.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="M21" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5464</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S21" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="U21" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26AUG1260CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2518,6 +2518,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:06:32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2518,11 +2518,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:06:32</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2518,7 +2518,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:14:26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2518,11 +2518,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:14:26</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2518,7 +2518,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:16:48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2424,11 +2424,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:04:57</t>
-        </is>
-      </c>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,7 +2424,11 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:21:38</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2517,6 +2521,95 @@
       <c r="AC21" t="inlineStr">
         <is>
           <t>2026-08-24 14:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:21:38</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>966.05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="H22" t="n">
+        <v>960</v>
+      </c>
+      <c r="I22" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="L22" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="M22" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4149</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="S22" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="U22" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NSE:KFINTECH26AUG960CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2424,11 +2424,7 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:21:38</t>
-        </is>
-      </c>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2424,7 +2424,6 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2606,6 +2605,11 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>NSE:KFINTECH26AUG960CE</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:24:52</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,6 +2612,101 @@
           <t>2026-08-24 14:24:52</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:36:03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4093</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K23" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="L23" t="n">
+        <v>65</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1831</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="S23" t="n">
+        <v>44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>NSE:SIEMENS26AUG4100CE</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2424,6 +2424,16 @@
           <t>NSE:JSWSTEEL26AUG1300CE</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:38:01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2701,12 +2711,6 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2523,11 +2523,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:16:48</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2523,7 +2523,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:40:48</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2523,11 +2523,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:40:48</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2523,7 +2523,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:47:29</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1865,6 +1865,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:50:42</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2521,11 +2526,6 @@
       <c r="W21" t="inlineStr">
         <is>
           <t>NSE:LODHA26AUG1260CE</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:47:29</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1865,11 +1865,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:50:42</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2526,6 +2521,11 @@
       <c r="W21" t="inlineStr">
         <is>
           <t>NSE:LODHA26AUG1260CE</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:52:17</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2523,11 +2523,7 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-24 14:52:17</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -2523,7 +2523,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:57:02</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2711,6 +2711,101 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:04:57</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>11080</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I24" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="K24" t="n">
+        <v>460.52</v>
+      </c>
+      <c r="L24" t="n">
+        <v>490.18</v>
+      </c>
+      <c r="M24" t="n">
+        <v>529.72</v>
+      </c>
+      <c r="N24" t="n">
+        <v>121</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="S24" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="U24" t="n">
+        <v>25</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>NSE:BAJAJHLDNG26AUG11100CE</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -776,6 +776,11 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:06:34</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2800,12 +2805,6 @@
           <t>NSE:BAJAJHLDNG26AUG11100CE</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -776,11 +776,6 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-24 15:06:34</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1868,6 +1863,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>Target 2 Hit</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:08:11</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/signals_2026-08-24.xlsx
@@ -1865,11 +1865,7 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-08-24 15:08:11</t>
-        </is>
-      </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
